--- a/output/pdf_financials_xlsx/XTM.xlsx
+++ b/output/pdf_financials_xlsx/XTM.xlsx
@@ -1136,7 +1136,7 @@
         <v>-0.863412</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>2.456643</v>
+        <v>-2.456643</v>
       </c>
     </row>
     <row r="17">
@@ -1364,7 +1364,7 @@
         <v>-0.863412</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>2.456643</v>
+        <v>-2.456643</v>
       </c>
     </row>
     <row r="21">
@@ -1501,7 +1501,7 @@
         <v>-0.863412</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>2.456643</v>
+        <v>-2.456643</v>
       </c>
     </row>
     <row r="24">
@@ -1717,7 +1717,7 @@
         <v>-0.863412</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>2.456643</v>
+        <v>-2.456643</v>
       </c>
     </row>
     <row r="28">
@@ -1811,7 +1811,7 @@
         <v>-0.853816</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>2.463416</v>
+        <v>-2.44987</v>
       </c>
     </row>
     <row r="30">
@@ -1917,7 +1917,7 @@
         <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -4575,40 +4575,40 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.316699</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.316699</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.355699</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.395314</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.90676</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.27705</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0.27705</v>
+        <v>0.750701</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.4418</v>
+        <v>0.915451</v>
       </c>
       <c r="J92" s="3" t="n">
         <v>0.33065</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0.386085</v>
+        <v>0.541755</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0.404005</v>
+        <v>0.559675</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0.389595</v>
+        <v>0.393512</v>
       </c>
     </row>
     <row r="93">
@@ -7674,7 +7674,11 @@
           <t>Warrant reserve (note 8)</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -11086,7 +11090,11 @@
           <t>Share-based payment reserve 9(c)</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" t="inlineStr">
         <is>
           <t>-</t>
@@ -16408,7 +16416,11 @@
           <t>Share-based payment reserve 8(c)</t>
         </is>
       </c>
-      <c r="D137" t="inlineStr"/>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E137" s="5" t="n">
         <v>1.316699</v>
       </c>
@@ -26847,7 +26859,7 @@
         <v>-0.863412</v>
       </c>
       <c r="P278" s="5" t="n">
-        <v>2.456643</v>
+        <v>-2.456643</v>
       </c>
     </row>
     <row r="279">
@@ -39742,7 +39754,7 @@
         <v>-3.078567</v>
       </c>
       <c r="I448" s="5" t="n">
-        <v>1.434719</v>
+        <v>-1.434719</v>
       </c>
       <c r="J448" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/XTM.xlsx
+++ b/output/pdf_financials_xlsx/XTM.xlsx
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.523065</v>
+        <v>5.158769</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.507818</v>
+        <v>3.593875</v>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.505508</v>
+        <v>1.531882</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.594639</v>
+        <v>1.150649</v>
       </c>
       <c r="G10" s="1" t="inlineStr">
         <is>
@@ -839,10 +839,10 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.298138</v>
+        <v>0.903177</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.34768</v>
+        <v>0.15199</v>
       </c>
       <c r="J10" s="3" t="n">
         <v>0.404392</v>
@@ -864,10 +864,10 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>0.211443</v>
+        <v>-4.424261</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>0.820479</v>
+        <v>-2.265578</v>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.280813</v>
+        <v>-1.307187</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.483621</v>
+        <v>-1.039631</v>
       </c>
       <c r="G11" s="1" t="inlineStr">
         <is>
@@ -886,10 +886,10 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.298138</v>
+        <v>-0.903177</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0.34768</v>
+        <v>-0.15199</v>
       </c>
       <c r="J11" s="3" t="n">
         <v>-0.404392</v>
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.030784</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.018453</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.004274</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>0.003992</v>
       </c>
       <c r="G12" s="1" t="inlineStr">
         <is>
@@ -933,22 +933,22 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.002542</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.000904</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.000794</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.003498</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.007671</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.015129</v>
       </c>
     </row>
     <row r="13">
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-4.300733</v>
+        <v>-4.331517</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.835749</v>
+        <v>-1.854202</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -1691,10 +1691,10 @@
         </is>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-3.078567</v>
+        <v>-3.082841</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.196878</v>
+        <v>-0.20087</v>
       </c>
       <c r="G27" s="1" t="inlineStr">
         <is>
@@ -1702,22 +1702,22 @@
         </is>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.458672</v>
+        <v>0.45613</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>3.362204</v>
+        <v>3.3613</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-4.482505</v>
+        <v>-4.483299</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-2.281481</v>
+        <v>-2.284979</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.863412</v>
+        <v>-0.8710830000000001</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-2.456643</v>
+        <v>-2.471772</v>
       </c>
     </row>
     <row r="28">
@@ -1774,10 +1774,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-4.269445</v>
+        <v>-4.300229</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.816942</v>
+        <v>-1.835395</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -1785,10 +1785,10 @@
         </is>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-3.069514</v>
+        <v>-3.073788</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.190274</v>
+        <v>-0.194266</v>
       </c>
       <c r="G29" s="1" t="inlineStr">
         <is>
@@ -1796,22 +1796,22 @@
         </is>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.462228</v>
+        <v>0.459686</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>3.38489</v>
+        <v>3.383986</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-4.464225</v>
+        <v>-4.465019</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-2.268047</v>
+        <v>-2.271545</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.853816</v>
+        <v>-0.861487</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-2.44987</v>
+        <v>-2.464999</v>
       </c>
     </row>
     <row r="30">
@@ -1821,10 +1821,10 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
-        <v>-581.2659630664336</v>
+        <v>-585.4570678603909</v>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-136.7873299420235</v>
+        <v>-138.1765523824867</v>
       </c>
       <c r="D30" s="1" t="inlineStr">
         <is>
@@ -1832,10 +1832,10 @@
         </is>
       </c>
       <c r="E30" s="3" t="n">
-        <v>-1366.080242105966</v>
+        <v>-1367.982376109838</v>
       </c>
       <c r="F30" s="3" t="n">
-        <v>-171.3902250085572</v>
+        <v>-174.9860383000955</v>
       </c>
       <c r="G30" s="1" t="inlineStr">
         <is>
@@ -1993,40 +1993,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.565109</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>2.297929</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.616132</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.975429</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.155873</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.594104</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>1.54417</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.807171</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.354322</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.323719</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.189777</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.422217</v>
       </c>
     </row>
     <row r="35">
@@ -2079,40 +2079,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.04</v>
+        <v>2.605109</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.08</v>
+        <v>2.377929</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.065</v>
+        <v>1.681132</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.0525</v>
+        <v>1.027929</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.5875</v>
+        <v>1.743373</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.490583</v>
+        <v>1.084687</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>2.16229</v>
+        <v>3.70646</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>3.8898</v>
+        <v>6.696971</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.015</v>
+        <v>1.369322</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.015</v>
+        <v>1.338719</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.519775</v>
+        <v>0.709552</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>2</v>
+        <v>3.422217</v>
       </c>
     </row>
     <row r="37">
@@ -2595,40 +2595,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.824723</v>
+        <v>0.259614</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.417249</v>
+        <v>0.11932</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.690796</v>
+        <v>0.07466399999999999</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>1.044982</v>
+        <v>0.069553</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.223826</v>
+        <v>0.067953</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.662817</v>
+        <v>0.068713</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>1.610753</v>
+        <v>0.066583</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2.937446</v>
+        <v>0.130275</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>3.176521</v>
+        <v>1.822199</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2.34808</v>
+        <v>1.024361</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>1.328345</v>
+        <v>1.138568</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.816556</v>
+        <v>1.394339</v>
       </c>
     </row>
     <row r="49">
@@ -6568,7 +6568,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -10154,7 +10154,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
@@ -26252,7 +26252,7 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E270" s="5" t="n">
@@ -28752,7 +28752,7 @@
       </c>
       <c r="D304" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E304" s="5" t="n">

--- a/output/pdf_financials_xlsx/XTM.xlsx
+++ b/output/pdf_financials_xlsx/XTM.xlsx
@@ -1338,10 +1338,10 @@
         </is>
       </c>
       <c r="E20" s="3" t="n">
-        <v>-3.078567</v>
+        <v>-2.040864</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>-0.196878</v>
+        <v>-1.663276</v>
       </c>
       <c r="G20" s="1" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.0016</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -5377,13 +5377,13 @@
         <v>0</v>
       </c>
       <c r="I111" s="3" t="n">
-        <v>0</v>
+        <v>-0.073225</v>
       </c>
       <c r="J111" s="3" t="n">
-        <v>0</v>
+        <v>-0.002814</v>
       </c>
       <c r="K111" s="3" t="n">
-        <v>0</v>
+        <v>-0.0007</v>
       </c>
       <c r="L111" s="3" t="n">
         <v>0</v>
@@ -5500,13 +5500,13 @@
         <v>0</v>
       </c>
       <c r="G114" s="3" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="H114" s="3" t="n">
         <v>0</v>
       </c>
       <c r="I114" s="3" t="n">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="J114" s="3" t="n">
         <v>0</v>
@@ -5518,7 +5518,7 @@
         <v>0</v>
       </c>
       <c r="M114" s="3" t="n">
-        <v>0</v>
+        <v>-0.169002</v>
       </c>
     </row>
     <row r="115">
@@ -5534,34 +5534,34 @@
         <v>0</v>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.237655</v>
       </c>
       <c r="E115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.518942</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
       </c>
       <c r="H115" s="3" t="n">
-        <v>0</v>
+        <v>0.113751</v>
       </c>
       <c r="I115" s="3" t="n">
-        <v>0</v>
+        <v>1.936202</v>
       </c>
       <c r="J115" s="3" t="n">
-        <v>0</v>
+        <v>0.6916060000000001</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.615992</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.331541</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.251896</v>
       </c>
     </row>
     <row r="116">
@@ -6375,7 +6375,7 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.0016</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -6390,13 +6390,13 @@
         <v>0</v>
       </c>
       <c r="I134" s="3" t="n">
-        <v>0</v>
+        <v>-0.073225</v>
       </c>
       <c r="J134" s="3" t="n">
-        <v>0</v>
+        <v>-0.002814</v>
       </c>
       <c r="K134" s="3" t="n">
-        <v>0</v>
+        <v>-0.0007</v>
       </c>
       <c r="L134" s="3" t="n">
         <v>0</v>
@@ -6418,7 +6418,7 @@
         <v>-2.230892</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-0.797818</v>
+        <v>-0.799418</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-1.430166</v>
@@ -6433,13 +6433,13 @@
         <v>-0.8728320000000001</v>
       </c>
       <c r="I135" s="3" t="n">
-        <v>-0.836981</v>
+        <v>-0.910206</v>
       </c>
       <c r="J135" s="3" t="n">
-        <v>-2.126641</v>
+        <v>-2.129455</v>
       </c>
       <c r="K135" s="3" t="n">
-        <v>-1.617009</v>
+        <v>-1.617709</v>
       </c>
       <c r="L135" s="3" t="n">
         <v>-0.967341</v>
@@ -18034,7 +18034,11 @@
           <t>Purchase of marketable securities</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr"/>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>PurchaseOfInvestment</t>
+        </is>
+      </c>
       <c r="E159" t="inlineStr">
         <is>
           <t>-</t>
@@ -18106,7 +18110,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E160" t="inlineStr">
         <is>
           <t>-</t>
@@ -19392,7 +19400,11 @@
           <t>Purchase of equipment (note 7)</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr"/>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E178" t="inlineStr">
         <is>
           <t>-</t>
@@ -19844,7 +19856,11 @@
           <t>Proceed from short-term investment</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -22466,7 +22482,11 @@
           <t>Proceeds on sale of marketable securities 5</t>
         </is>
       </c>
-      <c r="D219" t="inlineStr"/>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E219" t="inlineStr">
         <is>
           <t>-</t>
@@ -24096,7 +24116,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr"/>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E241" t="inlineStr">
         <is>
           <t>-</t>
@@ -39506,7 +39530,11 @@
           <t>Net (loss) from continuing operations</t>
         </is>
       </c>
-      <c r="D445" t="inlineStr"/>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E445" t="inlineStr">
         <is>
           <t>-</t>
